--- a/11-management/历史归档/project-phase-progress.xlsx
+++ b/11-management/历史归档/project-phase-progress.xlsx
@@ -1483,67 +1483,67 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>P2-1 依赖清理+阻塞BUG修复</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>已完成（2026-09-19）</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>OpenCV 收敛为 2 包（4.10.0.84 同版本）；pynvml 21ms 替换 nvidia-smi 147ms；BUG-1 区域截图 / BUG-3 OCR 常驻已修并实跑验证</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>56 单测全绿；区域截图 [320,200]；OCR 冷启 8888ms / 推理 106ms</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="0" t="inlineStr">
         <is>
           <t>BUG-2 / BUG-4 移交 P2-2 收尾</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>P2-2 七层目录骨架（方案B迁移）</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>基本完成（暂停中）</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>P2-layers/contracts 9 文件 + env_adapter 7 文件已迁；P1 侧留 shim；基线 c66e5d9 已推远端</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>56 单测 OK（0.413s）；16 文件行数与迁移前逐一比对一致</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>收尾 5 项：#1 改调用方 import；#2 删 shim；#3 P1 目录改名；#4 feature flag；#5 BUG-2+BUG-4</t>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>✅ 已完成（2026-09-19，收尾 5 项闭环）</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>P2-layers 契约9+适配7 已迁；收尾：调用方import改P2-layers、删shim、目录改名P1-toolbox-legacy、feature flag restore_p1_shim.py、BUG-2接线/BUG-4修复</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>56 单测 5 次全绿；实跑验证（env_profile 入审计/framework 不再误判）</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>tag 未打（是否 ui-toolbox-P2-2 待用户）</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>—— 2026-09-19 18:4x 更新：追加第 9/10 两行；进度细则以 11-management/接下来的任务.txt（10 轮制）为准 ——</t>
         </is>
